--- a/image processing/chapter1.xlsx
+++ b/image processing/chapter1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D 資料匣\課程\勤益課程\數位影像\PPT\授課版_(教師專用)\excel\chapter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D 資料匣\課程\勤益課程\數位影像\image processing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB708BA1-FCD1-473D-81A0-1FDB995F67A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE7DA9EF-6605-4982-AAFF-532F62D9D8DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30970" yWindow="-2290" windowWidth="28800" windowHeight="15320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-6190" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="248">
   <si>
     <t>question</t>
   </si>
@@ -40,619 +40,19 @@
     <t>answer</t>
   </si>
   <si>
-    <t>數位影像處理技術最早應用於哪個領域？</t>
-  </si>
-  <si>
-    <t>太空探測</t>
-  </si>
-  <si>
-    <t>醫學影像</t>
-  </si>
-  <si>
-    <t>電影製作</t>
-  </si>
-  <si>
-    <t>軍事偵察</t>
-  </si>
-  <si>
-    <t>第一張數位影像是在哪一年產生的？</t>
-  </si>
-  <si>
-    <t>1957年</t>
-  </si>
-  <si>
-    <t>1980年</t>
-  </si>
-  <si>
-    <t>1964年</t>
-  </si>
-  <si>
-    <t>1970年</t>
-  </si>
-  <si>
-    <t>CCD（電荷耦合元件）是由哪家公司發明的？</t>
-  </si>
-  <si>
-    <t>貝爾實驗室</t>
-  </si>
-  <si>
-    <t>蘋果</t>
-  </si>
-  <si>
-    <t>IBM</t>
-  </si>
-  <si>
-    <t>微軟</t>
-  </si>
-  <si>
-    <t>數位影像的基本單位稱為？</t>
-  </si>
-  <si>
-    <t>向量</t>
-  </si>
-  <si>
     <t>像素</t>
   </si>
   <si>
-    <t>矩陣</t>
-  </si>
-  <si>
-    <t>位元</t>
-  </si>
-  <si>
-    <t>RGB色彩模式中，R代表什麼顏色？</t>
-  </si>
-  <si>
-    <t>紅色</t>
-  </si>
-  <si>
-    <t>綠色</t>
-  </si>
-  <si>
-    <t>黃色</t>
-  </si>
-  <si>
-    <t>藍色</t>
-  </si>
-  <si>
-    <t>影像解析度通常以什麼單位表示？</t>
-  </si>
-  <si>
-    <t>Hz</t>
-  </si>
-  <si>
-    <t>MB</t>
-  </si>
-  <si>
-    <t>dpi</t>
-  </si>
-  <si>
-    <t>CPU</t>
-  </si>
-  <si>
-    <t>8位元灰階影像可以表示多少種灰度等級？</t>
-  </si>
-  <si>
-    <t>1024</t>
-  </si>
-  <si>
-    <t>512</t>
-  </si>
-  <si>
-    <t>256</t>
-  </si>
-  <si>
-    <t>128</t>
-  </si>
-  <si>
-    <t>JPEG是一種什麼類型的影像壓縮格式？</t>
-  </si>
-  <si>
-    <t>失真壓縮</t>
-  </si>
-  <si>
-    <t>無損壓縮</t>
-  </si>
-  <si>
-    <t>向量壓縮</t>
-  </si>
-  <si>
-    <t>不壓縮</t>
-  </si>
-  <si>
-    <t>下列哪種不是常見的影像檔案格式？</t>
-  </si>
-  <si>
-    <t>PNG</t>
-  </si>
-  <si>
-    <t>MP3</t>
-  </si>
-  <si>
-    <t>GIF</t>
-  </si>
-  <si>
-    <t>BMP</t>
-  </si>
-  <si>
-    <t>影像的空間解析度是指？</t>
-  </si>
-  <si>
-    <t>顏色數量</t>
-  </si>
-  <si>
-    <t>像素密度</t>
-  </si>
-  <si>
-    <t>壓縮比率</t>
-  </si>
-  <si>
     <t>檔案大小</t>
   </si>
   <si>
-    <t>CMY色彩模式主要用於？</t>
-  </si>
-  <si>
-    <t>印刷輸出</t>
-  </si>
-  <si>
-    <t>紅外線影像</t>
-  </si>
-  <si>
-    <t>螢幕顯示</t>
-  </si>
-  <si>
-    <t>數位影像處理的主要目的不包括？</t>
-  </si>
-  <si>
-    <t>影像增強</t>
-  </si>
-  <si>
     <t>影像壓縮</t>
   </si>
   <si>
-    <t>影像加密</t>
-  </si>
-  <si>
-    <t>影像還原</t>
-  </si>
-  <si>
-    <t>灰階影像中，0通常代表？</t>
-  </si>
-  <si>
-    <t>透明</t>
-  </si>
-  <si>
-    <t>黑色</t>
-  </si>
-  <si>
-    <t>白色</t>
-  </si>
-  <si>
-    <t>灰色</t>
-  </si>
-  <si>
-    <t>真彩色影像通常使用多少位元表示？</t>
-  </si>
-  <si>
-    <t>16位元</t>
-  </si>
-  <si>
-    <t>8位元</t>
-  </si>
-  <si>
-    <t>32位元</t>
-  </si>
-  <si>
-    <t>24位元</t>
-  </si>
-  <si>
-    <t>影像取樣是指？</t>
-  </si>
-  <si>
-    <t>亮度量化</t>
-  </si>
-  <si>
-    <t>空間離散化</t>
-  </si>
-  <si>
-    <t>色彩轉換</t>
-  </si>
-  <si>
-    <t>影像量化是指？</t>
-  </si>
-  <si>
-    <t>色彩混合</t>
-  </si>
-  <si>
-    <t>影像旋轉</t>
-  </si>
-  <si>
-    <t>灰度離散化</t>
-  </si>
-  <si>
-    <t>下列哪個不是影像的基本屬性？</t>
-  </si>
-  <si>
-    <t>色彩深度</t>
-  </si>
-  <si>
-    <t>檔案格式</t>
-  </si>
-  <si>
-    <t>處理速度</t>
-  </si>
-  <si>
     <t>解析度</t>
   </si>
   <si>
-    <t>PNG格式的主要優點是？</t>
-  </si>
-  <si>
-    <t>處理最快</t>
-  </si>
-  <si>
-    <t>檔案最小</t>
-  </si>
-  <si>
-    <t>相容性最差</t>
-  </si>
-  <si>
-    <t>支援透明度</t>
-  </si>
-  <si>
-    <t>影像直方圖主要顯示什麼資訊？</t>
-  </si>
-  <si>
-    <t>影像大小</t>
-  </si>
-  <si>
-    <t>灰度分布</t>
-  </si>
-  <si>
-    <t>二值化影像只包含幾種顏色？</t>
-  </si>
-  <si>
-    <t>4種</t>
-  </si>
-  <si>
-    <t>8種</t>
-  </si>
-  <si>
-    <t>2種</t>
-  </si>
-  <si>
-    <t>1種</t>
-  </si>
-  <si>
-    <t>影像的長寬比稱為？</t>
-  </si>
-  <si>
-    <t>寬高比</t>
-  </si>
-  <si>
-    <t>壓縮比</t>
-  </si>
-  <si>
-    <t>像素比</t>
-  </si>
-  <si>
-    <t>YUV色彩空間主要用於？</t>
-  </si>
-  <si>
-    <t>印刷</t>
-  </si>
-  <si>
-    <t>衛星影像</t>
-  </si>
-  <si>
-    <t>視訊編碼</t>
-  </si>
-  <si>
-    <t>影像的位元深度決定了？</t>
-  </si>
-  <si>
-    <t>壓縮效率</t>
-  </si>
-  <si>
-    <t>可表示的顏色數</t>
-  </si>
-  <si>
-    <t>GIF格式最多支援多少種顏色？</t>
-  </si>
-  <si>
-    <t>1677萬色</t>
-  </si>
-  <si>
-    <t>16色</t>
-  </si>
-  <si>
-    <t>65536色</t>
-  </si>
-  <si>
-    <t>256色</t>
-  </si>
-  <si>
-    <t>影像的對比度是指？</t>
-  </si>
-  <si>
-    <t>明暗差異</t>
-  </si>
-  <si>
-    <t>顏色種類</t>
-  </si>
-  <si>
-    <t>RAW格式影像的特點是？</t>
-  </si>
-  <si>
-    <t>相容性好</t>
-  </si>
-  <si>
-    <t>壓縮率高</t>
-  </si>
-  <si>
-    <t>未經處理</t>
-  </si>
-  <si>
-    <t>影像的銳利度主要與什麼有關？</t>
-  </si>
-  <si>
-    <t>邊緣清晰度</t>
-  </si>
-  <si>
-    <t>HSV色彩模式中，H代表？</t>
-  </si>
-  <si>
-    <t>對比度</t>
-  </si>
-  <si>
-    <t>飽和度</t>
-  </si>
-  <si>
-    <t>色相</t>
-  </si>
-  <si>
-    <t>亮度</t>
-  </si>
-  <si>
-    <t>影像的雜訊通常來自？</t>
-  </si>
-  <si>
-    <t>顯示器</t>
-  </si>
-  <si>
-    <t>儲存裝置</t>
-  </si>
-  <si>
-    <t>感測器</t>
-  </si>
-  <si>
-    <t>壓縮過程</t>
-  </si>
-  <si>
-    <t>TIFF格式的主要特點是？</t>
-  </si>
-  <si>
-    <t>支援多種色彩模式</t>
-  </si>
-  <si>
-    <t>高壓縮率</t>
-  </si>
-  <si>
-    <t>影像的動態範圍是指？</t>
-  </si>
-  <si>
-    <t>最亮與最暗的比值</t>
-  </si>
-  <si>
-    <t>色彩種類</t>
-  </si>
-  <si>
-    <t>索引色影像使用什麼來儲存顏色資訊？</t>
-  </si>
-  <si>
-    <t>CMYK值</t>
-  </si>
-  <si>
-    <t>RGB值</t>
-  </si>
-  <si>
-    <t>調色盤</t>
-  </si>
-  <si>
-    <t>HSV值</t>
-  </si>
-  <si>
-    <t>影像的色彩飽和度是指？</t>
-  </si>
-  <si>
-    <t>顏色的對比</t>
-  </si>
-  <si>
-    <t>顏色的純度</t>
-  </si>
-  <si>
-    <t>顏色的亮度</t>
-  </si>
-  <si>
-    <t>顏色的數量</t>
-  </si>
-  <si>
-    <t>BMP格式的主要缺點是？</t>
-  </si>
-  <si>
-    <t>檔案過大</t>
-  </si>
-  <si>
-    <t>失真嚴重</t>
-  </si>
-  <si>
-    <t>不支援彩色</t>
-  </si>
-  <si>
-    <t>相容性差</t>
-  </si>
-  <si>
-    <t>影像的伽瑪校正主要用於？</t>
-  </si>
-  <si>
-    <t>改變色彩</t>
-  </si>
-  <si>
-    <t>調整亮度</t>
-  </si>
-  <si>
-    <t>壓縮影像</t>
-  </si>
-  <si>
-    <t>旋轉影像</t>
-  </si>
-  <si>
-    <t>WebP格式是由哪家公司開發的？</t>
-  </si>
-  <si>
-    <t>Google</t>
-  </si>
-  <si>
-    <t>Adobe</t>
-  </si>
-  <si>
-    <t>影像的色域是指？</t>
-  </si>
-  <si>
-    <t>可表示的顏色範圍</t>
-  </si>
-  <si>
-    <t>EXIF資訊主要儲存什麼？</t>
-  </si>
-  <si>
-    <t>顯示設定</t>
-  </si>
-  <si>
-    <t>壓縮演算法</t>
-  </si>
-  <si>
-    <t>影像內容</t>
-  </si>
-  <si>
-    <t>拍攝參數</t>
-  </si>
-  <si>
-    <t>影像的色溫主要影響？</t>
-  </si>
-  <si>
-    <t>色彩偏向</t>
-  </si>
-  <si>
-    <t>向量圖形與點陣圖形的主要差異是？</t>
-  </si>
-  <si>
-    <t>縮放特性</t>
-  </si>
-  <si>
-    <t>色彩數量</t>
-  </si>
-  <si>
-    <t>影像的白平衡主要用於？</t>
-  </si>
-  <si>
-    <t>增加對比</t>
-  </si>
-  <si>
-    <t>銳化影像</t>
-  </si>
-  <si>
-    <t>校正色溫</t>
-  </si>
-  <si>
-    <t>HDR影像的主要特點是？</t>
-  </si>
-  <si>
-    <t>檔案小</t>
-  </si>
-  <si>
-    <t>高動態範圍</t>
-  </si>
-  <si>
-    <t>處理快</t>
-  </si>
-  <si>
-    <t>影像的色彩深度與什麼直接相關？</t>
-  </si>
-  <si>
-    <t>位元數</t>
-  </si>
-  <si>
-    <t>壓縮率</t>
-  </si>
-  <si>
-    <t>JPEG 2000相較於JPEG的主要改進是？</t>
-  </si>
-  <si>
-    <t>更小檔案</t>
-  </si>
-  <si>
-    <t>更簡單格式</t>
-  </si>
-  <si>
-    <t>更快處理</t>
-  </si>
-  <si>
-    <t>更好壓縮品質</t>
-  </si>
-  <si>
-    <t>影像的曝光值主要影響？</t>
-  </si>
-  <si>
     <t>色彩</t>
-  </si>
-  <si>
-    <t>Alpha通道主要用於表示？</t>
-  </si>
-  <si>
-    <t>透明度</t>
-  </si>
-  <si>
-    <t>影像的ISO值越高表示？</t>
-  </si>
-  <si>
-    <t>感光度越高</t>
-  </si>
-  <si>
-    <t>色彩越多</t>
-  </si>
-  <si>
-    <t>解析度越高</t>
-  </si>
-  <si>
-    <t>檔案越大</t>
-  </si>
-  <si>
-    <t>色彩空間轉換主要用於？</t>
-  </si>
-  <si>
-    <t>增加解析度</t>
-  </si>
-  <si>
-    <t>不同裝置間的色彩一致性</t>
-  </si>
-  <si>
-    <t>減少雜訊</t>
-  </si>
-  <si>
-    <t>影像的光圈值主要影響？</t>
-  </si>
-  <si>
-    <t>景深</t>
-  </si>
-  <si>
-    <t>無損壓縮的主要優點是？</t>
-  </si>
-  <si>
-    <t>壓縮率最高</t>
-  </si>
-  <si>
-    <t>不損失資訊</t>
   </si>
   <si>
     <t>title</t>
@@ -667,6 +67,705 @@
   <si>
     <t>CH 01 數位影像起源與發展</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>數位影像處理的英文縮寫為何？</t>
+  </si>
+  <si>
+    <t>DIP</t>
+  </si>
+  <si>
+    <t>DPI</t>
+  </si>
+  <si>
+    <t>IPD</t>
+  </si>
+  <si>
+    <t>PDI</t>
+  </si>
+  <si>
+    <t>數位影像處理的核心目的是什麼？</t>
+  </si>
+  <si>
+    <t>提取、分析、理解和視覺化影像資訊</t>
+  </si>
+  <si>
+    <t>壓縮影像檔案大小</t>
+  </si>
+  <si>
+    <t>提高影像解析度</t>
+  </si>
+  <si>
+    <t>減少影像雜訊</t>
+  </si>
+  <si>
+    <t>數位影像中的最小單位稱為什麼？</t>
+  </si>
+  <si>
+    <t>位元組</t>
+  </si>
+  <si>
+    <t>每個像素都具有什麼特定的屬性？</t>
+  </si>
+  <si>
+    <t>大小</t>
+  </si>
+  <si>
+    <t>溫度</t>
+  </si>
+  <si>
+    <t>形狀</t>
+  </si>
+  <si>
+    <t>強度（亮度）</t>
+  </si>
+  <si>
+    <t>數位影像可以在哪裡進行讀取與儲存？</t>
+  </si>
+  <si>
+    <t>紙張上</t>
+  </si>
+  <si>
+    <t>膠卷中</t>
+  </si>
+  <si>
+    <t>電腦中</t>
+  </si>
+  <si>
+    <t>底片上</t>
+  </si>
+  <si>
+    <t>數位影像處理技術面臨的三大挑戰不包括下列何者？</t>
+  </si>
+  <si>
+    <t>影像解析度的選擇</t>
+  </si>
+  <si>
+    <t>隱私安全</t>
+  </si>
+  <si>
+    <t>即時性的處理</t>
+  </si>
+  <si>
+    <t>影像色彩的選擇</t>
+  </si>
+  <si>
+    <t>高解析度的影像檔案通常具有什麼特性？</t>
+  </si>
+  <si>
+    <t>檔案非常小</t>
+  </si>
+  <si>
+    <t>不需壓縮</t>
+  </si>
+  <si>
+    <t>處理速度快</t>
+  </si>
+  <si>
+    <t>檔案非常大</t>
+  </si>
+  <si>
+    <t>傳輸大型影像檔案可能會造成什麼問題？</t>
+  </si>
+  <si>
+    <t>耗時並增加系統負載</t>
+  </si>
+  <si>
+    <t>提高影像品質</t>
+  </si>
+  <si>
+    <t>減少儲存空間</t>
+  </si>
+  <si>
+    <t>加快處理速度</t>
+  </si>
+  <si>
+    <t>極端壓縮影像可以改善什麼問題？</t>
+  </si>
+  <si>
+    <t>影像品質</t>
+  </si>
+  <si>
+    <t>影像解析度</t>
+  </si>
+  <si>
+    <t>即時傳輸與即時處理</t>
+  </si>
+  <si>
+    <t>色彩飽和度</t>
+  </si>
+  <si>
+    <t>壓縮後的影像可能導致什麼問題？</t>
+  </si>
+  <si>
+    <t>檔案變大</t>
+  </si>
+  <si>
+    <t>色彩變多</t>
+  </si>
+  <si>
+    <t>處理速度變慢</t>
+  </si>
+  <si>
+    <t>影像品質下降</t>
+  </si>
+  <si>
+    <t>數位影像處理中，Real-Time 的中文意思是什麼？</t>
+  </si>
+  <si>
+    <t>即時</t>
+  </si>
+  <si>
+    <t>真實時間</t>
+  </si>
+  <si>
+    <t>延遲處理</t>
+  </si>
+  <si>
+    <t>批次處理</t>
+  </si>
+  <si>
+    <t>影像處理技術在產業界的需求趨勢為何？</t>
+  </si>
+  <si>
+    <t>即時或接近即時處理</t>
+  </si>
+  <si>
+    <t>手動處理</t>
+  </si>
+  <si>
+    <t>數位影像相較於傳統影像，在哪方面具有優勢？</t>
+  </si>
+  <si>
+    <t>可使用軟體精確修改</t>
+  </si>
+  <si>
+    <t>成本較低</t>
+  </si>
+  <si>
+    <t>不需要電腦</t>
+  </si>
+  <si>
+    <t>保存時間較短</t>
+  </si>
+  <si>
+    <t>影像處理的三大挑戰就像玩什麼遊戲一樣需要找平衡？</t>
+  </si>
+  <si>
+    <t>跳繩</t>
+  </si>
+  <si>
+    <t>籃球</t>
+  </si>
+  <si>
+    <t>翹翹板</t>
+  </si>
+  <si>
+    <t>足球</t>
+  </si>
+  <si>
+    <t>在影像處理中，Pixels 的中文是什麼？</t>
+  </si>
+  <si>
+    <t>畫素</t>
+  </si>
+  <si>
+    <t>點素</t>
+  </si>
+  <si>
+    <t>圖素</t>
+  </si>
+  <si>
+    <t>數位影像處理可以使用什麼來分析和處理影像？</t>
+  </si>
+  <si>
+    <t>軟體</t>
+  </si>
+  <si>
+    <t>硬體</t>
+  </si>
+  <si>
+    <t>人工</t>
+  </si>
+  <si>
+    <t>化學藥劑</t>
+  </si>
+  <si>
+    <t>影像壓縮的主要目的是什麼？</t>
+  </si>
+  <si>
+    <t>增加色彩</t>
+  </si>
+  <si>
+    <t>減少檔案大小</t>
+  </si>
+  <si>
+    <t>提高解析度</t>
+  </si>
+  <si>
+    <t>數位影像處理技術中，儲存、傳輸和壓縮屬於什麼問題？</t>
+  </si>
+  <si>
+    <t>次要問題</t>
+  </si>
+  <si>
+    <t>未來問題</t>
+  </si>
+  <si>
+    <t>無關問題</t>
+  </si>
+  <si>
+    <t>核心問題</t>
+  </si>
+  <si>
+    <t>影像資訊遺失可能影響什麼？</t>
+  </si>
+  <si>
+    <t>後續的影像分析和處理</t>
+  </si>
+  <si>
+    <t>傳輸速度</t>
+  </si>
+  <si>
+    <t>儲存成本</t>
+  </si>
+  <si>
+    <t>數位照片包含大量的什麼？</t>
+  </si>
+  <si>
+    <t>顏色</t>
+  </si>
+  <si>
+    <t>檔案</t>
+  </si>
+  <si>
+    <t>資料夾</t>
+  </si>
+  <si>
+    <t>在影像處理中，隨著收集的影像資料越來越多，主要面臨的挑戰是什麼？</t>
+  </si>
+  <si>
+    <t>如何刪除資料</t>
+  </si>
+  <si>
+    <t>如何降低影像品質</t>
+  </si>
+  <si>
+    <t>如何減少影像數量</t>
+  </si>
+  <si>
+    <t>如何有效、快速地處理和分析資料</t>
+  </si>
+  <si>
+    <t>機器學習和深度學習在影像處理中應用增多後，產生的主要挑戰是什麼？</t>
+  </si>
+  <si>
+    <t>資料標註和資料隱私</t>
+  </si>
+  <si>
+    <t>硬體成本</t>
+  </si>
+  <si>
+    <t>軟體授權</t>
+  </si>
+  <si>
+    <t>網路頻寬</t>
+  </si>
+  <si>
+    <t>大資料分析在影像處理中的主要目標是什麼？</t>
+  </si>
+  <si>
+    <t>增加資料量</t>
+  </si>
+  <si>
+    <t>減少運算時間</t>
+  </si>
+  <si>
+    <t>提取有價值的資訊並做出有意義的預測或決策</t>
+  </si>
+  <si>
+    <t>降低儲存成本</t>
+  </si>
+  <si>
+    <t>影像壓縮與影像品質之間的關係為何？</t>
+  </si>
+  <si>
+    <t>壓縮越多品質越好</t>
+  </si>
+  <si>
+    <t>壓縮不影響品質</t>
+  </si>
+  <si>
+    <t>兩者無關</t>
+  </si>
+  <si>
+    <t>壓縮可能導致品質下降</t>
+  </si>
+  <si>
+    <t>數位影像處理技術的核心優勢在於能夠進行什麼樣的修改？</t>
+  </si>
+  <si>
+    <t>精確修改</t>
+  </si>
+  <si>
+    <t>隨機修改</t>
+  </si>
+  <si>
+    <t>模糊修改</t>
+  </si>
+  <si>
+    <t>自動修改</t>
+  </si>
+  <si>
+    <t>在傳統和數位影像之間，哪三個是核心問題？</t>
+  </si>
+  <si>
+    <t>色彩、亮度、對比</t>
+  </si>
+  <si>
+    <t>大小、形狀、位置</t>
+  </si>
+  <si>
+    <t>儲存、傳輸和壓縮</t>
+  </si>
+  <si>
+    <t>時間、空間、頻率</t>
+  </si>
+  <si>
+    <t>即時處理環境對影像分析的要求是什麼？</t>
+  </si>
+  <si>
+    <t>可以延遲處理</t>
+  </si>
+  <si>
+    <t>批次處理即可</t>
+  </si>
+  <si>
+    <t>需要即時或接近即時處理</t>
+  </si>
+  <si>
+    <t>影像處理中的「平衡」概念主要指的是什麼？</t>
+  </si>
+  <si>
+    <t>在解析度、隱私安全、即時性之間取得平衡</t>
+  </si>
+  <si>
+    <t>色彩平衡</t>
+  </si>
+  <si>
+    <t>亮度平衡</t>
+  </si>
+  <si>
+    <t>對比度平衡</t>
+  </si>
+  <si>
+    <t>數位影像處理提供了什麼樣的手段？</t>
+  </si>
+  <si>
+    <t>簡單的手段</t>
+  </si>
+  <si>
+    <t>複雜的手段</t>
+  </si>
+  <si>
+    <t>強大的手段</t>
+  </si>
+  <si>
+    <t>昂貴的手段</t>
+  </si>
+  <si>
+    <t>影像分析的最終目的通常包括什麼？</t>
+  </si>
+  <si>
+    <t>增加檔案大小</t>
+  </si>
+  <si>
+    <t>減少色彩</t>
+  </si>
+  <si>
+    <t>降低解析度</t>
+  </si>
+  <si>
+    <t>理解和視覺化資訊</t>
+  </si>
+  <si>
+    <t>在極端壓縮情況下，雖然可以改善即時傳輸，但會產生什麼負面影響？</t>
+  </si>
+  <si>
+    <t>影像資訊遺失導致品質下降</t>
+  </si>
+  <si>
+    <t>提高運算成本</t>
+  </si>
+  <si>
+    <t>增加傳輸時間</t>
+  </si>
+  <si>
+    <t>數位影像處理技術面臨的挑戰可以簡化為幾大項目？</t>
+  </si>
+  <si>
+    <t>兩大項目</t>
+  </si>
+  <si>
+    <t>四大項目</t>
+  </si>
+  <si>
+    <t>三大項目</t>
+  </si>
+  <si>
+    <t>五大項目</t>
+  </si>
+  <si>
+    <t>影像處理中的資料隱私挑戰主要與什麼技術的應用有關？</t>
+  </si>
+  <si>
+    <t>傳統影像處理</t>
+  </si>
+  <si>
+    <t>影像儲存</t>
+  </si>
+  <si>
+    <t>機器學習和深度學習</t>
+  </si>
+  <si>
+    <t>數位影像的每個像素具有特定的什麼屬性，這對影像處理很重要？</t>
+  </si>
+  <si>
+    <t>位置</t>
+  </si>
+  <si>
+    <t>影像處理技術在產業界的應用趨勢是朝向什麼方向發展？</t>
+  </si>
+  <si>
+    <t>離線批次處理</t>
+  </si>
+  <si>
+    <t>即時處理和大資料分析</t>
+  </si>
+  <si>
+    <t>簡化處理</t>
+  </si>
+  <si>
+    <t>數位影像相較於傳統影像，在儲存方面有什麼特點？</t>
+  </si>
+  <si>
+    <t>需要實體空間</t>
+  </si>
+  <si>
+    <t>容易損壞</t>
+  </si>
+  <si>
+    <t>需要特殊設備</t>
+  </si>
+  <si>
+    <t>可以輕鬆在電腦中進行讀取與儲存</t>
+  </si>
+  <si>
+    <t>影像壓縮後可能影響什麼後續工作？</t>
+  </si>
+  <si>
+    <t>影像拍攝</t>
+  </si>
+  <si>
+    <t>影像分析和處理</t>
+  </si>
+  <si>
+    <t>影像刪除</t>
+  </si>
+  <si>
+    <t>影像複製</t>
+  </si>
+  <si>
+    <t>大資料分析在影像處理中越來越受重視的原因是什麼？</t>
+  </si>
+  <si>
+    <t>影像資料越來越少</t>
+  </si>
+  <si>
+    <t>收集的影像資料越來越多</t>
+  </si>
+  <si>
+    <t>處理速度越來越慢</t>
+  </si>
+  <si>
+    <t>儲存成本越來越高</t>
+  </si>
+  <si>
+    <t>數位影像處理的核心在於提供什麼樣的能力？</t>
+  </si>
+  <si>
+    <t>拍攝影像</t>
+  </si>
+  <si>
+    <t>刪除影像</t>
+  </si>
+  <si>
+    <t>複製影像</t>
+  </si>
+  <si>
+    <t>影像處理中的即時性挑戰主要來自於什麼需求？</t>
+  </si>
+  <si>
+    <t>降低成本</t>
+  </si>
+  <si>
+    <t>產業界希望即時或接近即時處理</t>
+  </si>
+  <si>
+    <t>減少人力</t>
+  </si>
+  <si>
+    <t>簡化流程</t>
+  </si>
+  <si>
+    <t>在影像處理技術的三大挑戰中，為何說它們像「翹翹板」一樣需要平衡？</t>
+  </si>
+  <si>
+    <t>因為它們互不相關</t>
+  </si>
+  <si>
+    <t>因為改善一項可能會影響其他項目，需要權衡取捨</t>
+  </si>
+  <si>
+    <t>因為它們都很簡單</t>
+  </si>
+  <si>
+    <t>因為它們可以同時解決</t>
+  </si>
+  <si>
+    <t>在即時影像處理的應用場景中，極端壓縮技術的使用體現了什麼樣的權衡策略？</t>
+  </si>
+  <si>
+    <t>犧牲儲存空間換取處理速度</t>
+  </si>
+  <si>
+    <t>犧牲影像品質換取即時傳輸能力</t>
+  </si>
+  <si>
+    <t>犧牲系統穩定性換取高解析度</t>
+  </si>
+  <si>
+    <t>犧牲安全性換取便利性</t>
+  </si>
+  <si>
+    <t>機器學習和深度學習在影像處理中的應用，為何會帶來資料標註的挑戰？</t>
+  </si>
+  <si>
+    <t>因為不需要訓練資料</t>
+  </si>
+  <si>
+    <t>因為需要大量準確標註的訓練資料，這需要人力和時間成本</t>
+  </si>
+  <si>
+    <t>因為演算法太簡單</t>
+  </si>
+  <si>
+    <t>因為硬體不足</t>
+  </si>
+  <si>
+    <t>在大資料影像分析中，「提取有價值的資訊並做出有意義的預測或決策」這個目標，主要挑戰在於什麼？</t>
+  </si>
+  <si>
+    <t>資料太少</t>
+  </si>
+  <si>
+    <t>如何在海量資料中快速找到關鍵模式和洞察</t>
+  </si>
+  <si>
+    <t>硬體太貴</t>
+  </si>
+  <si>
+    <t>軟體太複雜</t>
+  </si>
+  <si>
+    <t>數位影像處理技術的發展，為何使得「隱私安全」成為重要挑戰？</t>
+  </si>
+  <si>
+    <t>因為影像不包含個人資訊</t>
+  </si>
+  <si>
+    <t>因為影像可能包含敏感資訊，且處理和分析技術越強大，隱私風險越高</t>
+  </si>
+  <si>
+    <t>因為技術太簡單</t>
+  </si>
+  <si>
+    <t>因為沒有法律規範</t>
+  </si>
+  <si>
+    <t>在選擇影像解析度時，需要考慮哪些因素的平衡？</t>
+  </si>
+  <si>
+    <t>只考慮越高越好</t>
+  </si>
+  <si>
+    <t>需平衡儲存空間、傳輸效率、處理速度和應用需求</t>
+  </si>
+  <si>
+    <t>只考慮成本</t>
+  </si>
+  <si>
+    <t>只考慮美觀</t>
+  </si>
+  <si>
+    <t>影像壓縮導致的資訊遺失，對後續影像分析的影響主要體現在什麼方面？</t>
+  </si>
+  <si>
+    <t>完全沒有影響</t>
+  </si>
+  <si>
+    <t>可能降低分析準確度和細節識別能力</t>
+  </si>
+  <si>
+    <t>只影響檔案大小</t>
+  </si>
+  <si>
+    <t>只影響傳輸速度</t>
+  </si>
+  <si>
+    <t>數位影像處理技術的核心價值，從資訊處理的角度來看是什麼？</t>
+  </si>
+  <si>
+    <t>只是美化影像</t>
+  </si>
+  <si>
+    <t>將視覺資訊轉化為可分析、可理解的數據和知識</t>
+  </si>
+  <si>
+    <t>只是壓縮檔案</t>
+  </si>
+  <si>
+    <t>只是儲存影像</t>
+  </si>
+  <si>
+    <t>在即時影像處理系統中，為何傳輸大型檔案會「增加系統負載」？</t>
+  </si>
+  <si>
+    <t>因為檔案太小</t>
+  </si>
+  <si>
+    <t>因為需要更多頻寬、記憶體和處理資源，可能造成系統瓶頸</t>
+  </si>
+  <si>
+    <t>因為系統太強大</t>
+  </si>
+  <si>
+    <t>因為不需要處理</t>
+  </si>
+  <si>
+    <t>數位影像處理技術面臨的挑戰，反映了什麼樣的技術發展趨勢？</t>
+  </si>
+  <si>
+    <t>技術越來越簡單</t>
+  </si>
+  <si>
+    <t>在追求高品質、高效率、大規模應用的同時，需要解決資源限制和隱私安全等多維度問題</t>
+  </si>
+  <si>
+    <t>只需要提高硬體效能</t>
+  </si>
+  <si>
+    <t>不需要考慮實際應用</t>
   </si>
 </sst>
 </file>
@@ -1035,16 +1134,16 @@
   <sheetData>
     <row r="1" spans="1:6" ht="16.75" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>211</v>
+        <v>11</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>212</v>
+        <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>213</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>214</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
@@ -1069,19 +1168,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1089,19 +1188,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1109,119 +1208,119 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -1229,59 +1328,59 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D12" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="E13" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -1289,19 +1388,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E14" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F14">
         <v>3</v>
@@ -1309,99 +1408,99 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E15" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E16" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="D17" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E17" t="s">
-        <v>78</v>
+        <v>6</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D18" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E18" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D19" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E19" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F19">
         <v>3</v>
@@ -1409,19 +1508,19 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D20" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E20" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F20">
         <v>4</v>
@@ -1429,39 +1528,39 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C21" t="s">
-        <v>85</v>
+        <v>7</v>
       </c>
       <c r="D21" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E21" t="s">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B22" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C22" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D22" t="s">
-        <v>99</v>
+        <v>6</v>
       </c>
       <c r="E22" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F22">
         <v>3</v>
@@ -1469,59 +1568,59 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B23" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="C23" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E23" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B24" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C24" t="s">
-        <v>8</v>
+        <v>113</v>
       </c>
       <c r="D24" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="E24" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="F24">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="B25" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C25" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="D25" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="E25" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="F25">
         <v>3</v>
@@ -1529,19 +1628,19 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B26" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="C26" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D26" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="E26" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="F26">
         <v>4</v>
@@ -1549,39 +1648,39 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="D27" t="s">
-        <v>94</v>
+        <v>129</v>
       </c>
       <c r="E27" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="F27">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="B28" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="C28" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="D28" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="E28" t="s">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="F28">
         <v>3</v>
@@ -1589,59 +1688,59 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="B29" t="s">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="C29" t="s">
-        <v>125</v>
+        <v>69</v>
       </c>
       <c r="D29" t="s">
-        <v>52</v>
+        <v>138</v>
       </c>
       <c r="E29" t="s">
-        <v>54</v>
+        <v>139</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="B30" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="C30" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="D30" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="E30" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="B31" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="C31" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="D31" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="E31" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="F31">
         <v>3</v>
@@ -1649,59 +1748,59 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="B32" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="C32" t="s">
-        <v>90</v>
+        <v>152</v>
       </c>
       <c r="D32" t="s">
-        <v>89</v>
+        <v>153</v>
       </c>
       <c r="E32" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="B33" t="s">
-        <v>86</v>
+        <v>156</v>
       </c>
       <c r="C33" t="s">
-        <v>94</v>
+        <v>151</v>
       </c>
       <c r="D33" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="E33" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="F33">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="B34" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="C34" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="D34" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="E34" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="F34">
         <v>3</v>
@@ -1709,39 +1808,39 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="B35" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="C35" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="D35" t="s">
-        <v>150</v>
+        <v>8</v>
       </c>
       <c r="E35" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="F35">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="B36" t="s">
-        <v>153</v>
+        <v>31</v>
       </c>
       <c r="C36" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="D36" t="s">
-        <v>155</v>
+        <v>28</v>
       </c>
       <c r="E36" t="s">
-        <v>156</v>
+        <v>30</v>
       </c>
       <c r="F36">
         <v>1</v>
@@ -1749,179 +1848,179 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="B37" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="C37" t="s">
-        <v>159</v>
+        <v>69</v>
       </c>
       <c r="D37" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="E37" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="F37">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="B38" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="C38" t="s">
-        <v>20</v>
+        <v>176</v>
       </c>
       <c r="D38" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="E38" t="s">
-        <v>18</v>
+        <v>178</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="B39" t="s">
-        <v>54</v>
+        <v>180</v>
       </c>
       <c r="C39" t="s">
-        <v>94</v>
+        <v>181</v>
       </c>
       <c r="D39" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="E39" t="s">
-        <v>87</v>
+        <v>183</v>
       </c>
       <c r="F39">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="B40" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="C40" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="D40" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="E40" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="F40">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="B41" t="s">
-        <v>127</v>
+        <v>190</v>
       </c>
       <c r="C41" t="s">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="D41" t="s">
-        <v>94</v>
+        <v>191</v>
       </c>
       <c r="E41" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="F41">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="B42" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="C42" t="s">
-        <v>86</v>
+        <v>195</v>
       </c>
       <c r="D42" t="s">
-        <v>55</v>
+        <v>196</v>
       </c>
       <c r="E42" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="B43" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="C43" t="s">
-        <v>159</v>
+        <v>200</v>
       </c>
       <c r="D43" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="E43" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="F43">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="B44" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="C44" t="s">
-        <v>121</v>
+        <v>205</v>
       </c>
       <c r="D44" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="E44" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="F44">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="B45" t="s">
-        <v>94</v>
+        <v>209</v>
       </c>
       <c r="C45" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="D45" t="s">
-        <v>87</v>
+        <v>211</v>
       </c>
       <c r="E45" t="s">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="F45">
         <v>2</v>
@@ -1929,142 +2028,142 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="B46" t="s">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="C46" t="s">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="D46" t="s">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="E46" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="F46">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="B47" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="C47" t="s">
-        <v>87</v>
+        <v>220</v>
       </c>
       <c r="D47" t="s">
-        <v>127</v>
+        <v>221</v>
       </c>
       <c r="E47" t="s">
-        <v>130</v>
+        <v>222</v>
       </c>
       <c r="F47">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>195</v>
+        <v>223</v>
       </c>
       <c r="B48" t="s">
-        <v>127</v>
+        <v>224</v>
       </c>
       <c r="C48" t="s">
-        <v>130</v>
+        <v>225</v>
       </c>
       <c r="D48" t="s">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="E48" t="s">
-        <v>194</v>
+        <v>227</v>
       </c>
       <c r="F48">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="B49" t="s">
-        <v>198</v>
+        <v>229</v>
       </c>
       <c r="C49" t="s">
-        <v>199</v>
+        <v>230</v>
       </c>
       <c r="D49" t="s">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="E49" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="F49">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>202</v>
+        <v>233</v>
       </c>
       <c r="B50" t="s">
-        <v>160</v>
+        <v>234</v>
       </c>
       <c r="C50" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="D50" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
       <c r="E50" t="s">
-        <v>205</v>
+        <v>237</v>
       </c>
       <c r="F50">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="B51" t="s">
-        <v>87</v>
+        <v>239</v>
       </c>
       <c r="C51" t="s">
-        <v>194</v>
+        <v>240</v>
       </c>
       <c r="D51" t="s">
-        <v>55</v>
+        <v>241</v>
       </c>
       <c r="E51" t="s">
-        <v>207</v>
+        <v>242</v>
       </c>
       <c r="F51">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>208</v>
+        <v>243</v>
       </c>
       <c r="B52" t="s">
-        <v>90</v>
+        <v>244</v>
       </c>
       <c r="C52" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="D52" t="s">
-        <v>89</v>
+        <v>246</v>
       </c>
       <c r="E52" t="s">
-        <v>210</v>
+        <v>247</v>
       </c>
       <c r="F52">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
